--- a/public/templates/mailing-confirmation/mailing_confirmation.xlsx
+++ b/public/templates/mailing-confirmation/mailing_confirmation.xlsx
@@ -8,10 +8,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="郵送書類確認票" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-  </externalReferences>
   <definedNames>
     <definedName name="徽章1">INDIRECT(#REF!)</definedName>
     <definedName name="徽章2">INDIRECT('[2]請求書（前受金）行'!$R$10:$V$10)</definedName>
@@ -766,178 +762,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="入力元"/>
-      <sheetName val="簡易契約書 "/>
-      <sheetName val="簡易契約書 (行・司)"/>
-      <sheetName val="契約書★財産調査あり（連名）"/>
-      <sheetName val="契約書★財産調査なし（連名）"/>
-      <sheetName val="契約書★財産調査あり（行単独）"/>
-      <sheetName val="契約書(遺言など単独)★財産調査なし "/>
-      <sheetName val="委任状  (法定相続情報証明）"/>
-      <sheetName val="委任状"/>
-      <sheetName val="委任状（預金解約あり） "/>
-      <sheetName val="委任状 (登記のみ) "/>
-      <sheetName val="委任状 (遺言一般)"/>
-      <sheetName val="委任状 (贈与・信託)"/>
-      <sheetName val="委任状 (遺言検索のみ)"/>
-      <sheetName val="原本預かり証"/>
-      <sheetName val="原本受領証"/>
-      <sheetName val="郵送書類確認票"/>
-      <sheetName val="返送書類ご案内一覧 "/>
-      <sheetName val="契約書（1％）"/>
-      <sheetName val="契約書（執行）"/>
-      <sheetName val="請求書（前受金）行"/>
-      <sheetName val="請求書（前受金）司"/>
-      <sheetName val="立替実費"/>
-      <sheetName val="請求書 (確定)行"/>
-      <sheetName val="請求書 (確定) 司"/>
-      <sheetName val="領収書（前受金）行"/>
-      <sheetName val="領収書（前受金）司"/>
-      <sheetName val="領収書 (確定)行"/>
-      <sheetName val="領収書 (確定) 司"/>
-      <sheetName val="角２封筒"/>
-      <sheetName val="長形３号（白）"/>
-      <sheetName val="長形３号 (茶)"/>
-      <sheetName val="抽出元"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17" refreshError="1"/>
-      <sheetData sheetId="18" refreshError="1"/>
-      <sheetData sheetId="19" refreshError="1"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22" refreshError="1"/>
-      <sheetData sheetId="23"/>
-      <sheetData sheetId="24"/>
-      <sheetData sheetId="25" refreshError="1"/>
-      <sheetData sheetId="26" refreshError="1"/>
-      <sheetData sheetId="27" refreshError="1"/>
-      <sheetData sheetId="28" refreshError="1"/>
-      <sheetData sheetId="29" refreshError="1"/>
-      <sheetData sheetId="30" refreshError="1"/>
-      <sheetData sheetId="31" refreshError="1"/>
-      <sheetData sheetId="32" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="入力元"/>
-      <sheetName val="簡易契約書 "/>
-      <sheetName val="簡易契約書 (行・司)"/>
-      <sheetName val="契約書★財産調査あり（連名）"/>
-      <sheetName val="契約書★財産調査なし（連名）"/>
-      <sheetName val="契約書★財産調査あり（行単独）"/>
-      <sheetName val="契約書(遺言など単独)★財産調査なし "/>
-      <sheetName val="委任状  (法定相続情報証明）"/>
-      <sheetName val="委任状（行・司連名）"/>
-      <sheetName val="委任状（行・司連連名）預金解約あり"/>
-      <sheetName val="委任状（行・司連名）登記のみ"/>
-      <sheetName val="委任状（行のみ）相続"/>
-      <sheetName val="委任状 (司のみ)相続登記 "/>
-      <sheetName val="委任状 (行)遺言"/>
-      <sheetName val="委任状 (行司)贈与・信託"/>
-      <sheetName val="委任状 (司)贈与・信託 "/>
-      <sheetName val="委任状 (遺言検索のみ)"/>
-      <sheetName val="特定事務指示書（包括）"/>
-      <sheetName val="原本預かり証"/>
-      <sheetName val="原本受領証 "/>
-      <sheetName val="郵送書類確認票 (2)"/>
-      <sheetName val="郵送書類確認票"/>
-      <sheetName val="契約書（1％）"/>
-      <sheetName val="契約書（執行）"/>
-      <sheetName val="請求書（前受金）行"/>
-      <sheetName val="請求書（前受金）司"/>
-      <sheetName val="立替実費 行 "/>
-      <sheetName val="立替実費 司"/>
-      <sheetName val="請求書 (確定)行"/>
-      <sheetName val="請求書 (確定)司"/>
-      <sheetName val="領収書（前受金）行"/>
-      <sheetName val="領収書（前受金）司"/>
-      <sheetName val="領収書 (確定)行"/>
-      <sheetName val="領収書 (確定)司"/>
-      <sheetName val="角２封筒"/>
-      <sheetName val="長形３号（白）"/>
-      <sheetName val="長形３号 (茶)"/>
-      <sheetName val="Sheet7"/>
-      <sheetName val="抽出元"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22"/>
-      <sheetData sheetId="23"/>
-      <sheetData sheetId="24">
-        <row r="10">
-          <cell r="R10" t="str">
-            <v>行政書士法人</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="25"/>
-      <sheetData sheetId="26"/>
-      <sheetData sheetId="27"/>
-      <sheetData sheetId="28"/>
-      <sheetData sheetId="29"/>
-      <sheetData sheetId="30"/>
-      <sheetData sheetId="31"/>
-      <sheetData sheetId="32"/>
-      <sheetData sheetId="33"/>
-      <sheetData sheetId="34"/>
-      <sheetData sheetId="35"/>
-      <sheetData sheetId="36"/>
-      <sheetData sheetId="37"/>
-      <sheetData sheetId="38"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>

--- a/public/templates/mailing-confirmation/mailing_confirmation.xlsx
+++ b/public/templates/mailing-confirmation/mailing_confirmation.xlsx
@@ -19465,14 +19465,6 @@
     <mergeCell ref="I13:J13"/>
     <mergeCell ref="I9:J9"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation sqref="E27 J27" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>$N$23:$N$26</formula1>
-    </dataValidation>
-    <dataValidation sqref="I24" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>$N$18:$N$21</formula1>
-    </dataValidation>
-  </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9"/>
